--- a/AutoADA/templates/ProyectoPI_EstandarSenales&TAG.xlsx
+++ b/AutoADA/templates/ProyectoPI_EstandarSenales&TAG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://isaempresas-my.sharepoint.com/personal/asjimenez_intercolombia_com/Documents/Practica/AutomatismoADA/templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\OneDrive - INTERCONEXION ELECTRICA S.A. E.S.P\Practica\AutomatismoADA\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="8_{AF4DE4DD-A49C-4DDD-B6CB-B048BC4D7E01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E45CEA8D-5F96-41E1-975C-7667C46C40E0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C32762D-F075-4A8E-8092-3E4993BCAC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="684" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="684" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EstructuraTAG_PI" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Nombres de señales por empresas'!$A$2:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Senales_Analogas_Estado_SCADA!$A$2:$N$675</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Senales_Analogas_Estado_SCADA!$A$2:$N$676</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Senales_Digitales!$A$1:$D$73</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7527" uniqueCount="1756">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7603" uniqueCount="1774">
   <si>
     <t>ITCO:SCADA:CERR500:ATRAF01:I1</t>
   </si>
@@ -5367,13 +5367,67 @@
   </si>
   <si>
     <t>REP:PDC:CARA500:L-5001:dFREQ.Value</t>
+  </si>
+  <si>
+    <t>CONN</t>
+  </si>
+  <si>
+    <t>Estado de la linea</t>
+  </si>
+  <si>
+    <t>Lineas</t>
+  </si>
+  <si>
+    <t>PRES_ABS_SF6</t>
+  </si>
+  <si>
+    <t>PRES_ABS1_SF6</t>
+  </si>
+  <si>
+    <t>PRES_ABS2_SF6</t>
+  </si>
+  <si>
+    <t>PRES_ABS3_SF6</t>
+  </si>
+  <si>
+    <t>HUME_VOL_SF6</t>
+  </si>
+  <si>
+    <t>HUME_VOL1_SF6</t>
+  </si>
+  <si>
+    <t>HUME_VOL2_SF6</t>
+  </si>
+  <si>
+    <t>HUME_VOL3_SF6</t>
+  </si>
+  <si>
+    <t>ROCI1_SF6</t>
+  </si>
+  <si>
+    <t>ROCI2_SF6</t>
+  </si>
+  <si>
+    <t>ROCI3_SF6</t>
+  </si>
+  <si>
+    <t>ROCI_SF6</t>
+  </si>
+  <si>
+    <t>MOD_CAPAC</t>
+  </si>
+  <si>
+    <t>MOD_MONIT</t>
+  </si>
+  <si>
+    <t>MOD_INDUC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5482,6 +5536,12 @@
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -6454,10 +6514,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -6727,7 +6783,7 @@
   <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="40.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.54296875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.453125" customWidth="1"/>
     <col min="4" max="4" width="28.54296875" customWidth="1"/>
@@ -6774,7 +6830,7 @@
       <c r="E5" s="87"/>
       <c r="F5" s="87"/>
     </row>
-    <row r="6" spans="1:6" ht="0.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="0.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="87"/>
       <c r="B6" s="87"/>
       <c r="C6" s="87"/>
@@ -7078,20 +7134,20 @@
   <sheetPr>
     <tabColor theme="7" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:N675"/>
+  <dimension ref="A1:N699"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.6328125" style="83" customWidth="1"/>
-    <col min="2" max="2" width="31.36328125" style="56" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.54296875" style="56" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.54296875" style="83" customWidth="1"/>
+    <col min="2" max="2" width="31.453125" style="56" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="68.81640625" style="56" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="43.54296875" style="56" customWidth="1"/>
     <col min="5" max="5" width="21.54296875" style="56" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.36328125" style="56" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="26.36328125" style="56" customWidth="1"/>
-    <col min="11" max="11" width="11.90625" style="56" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.36328125" style="56" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.36328125" style="56" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="103.36328125" style="56" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.453125" style="56" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="26.453125" style="56" customWidth="1"/>
+    <col min="11" max="11" width="11.81640625" style="56" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.453125" style="56" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.453125" style="56" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="103.453125" style="56" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="11.453125" style="56"/>
   </cols>
   <sheetData>
@@ -19405,7 +19461,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="333" spans="1:14" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:14" ht="23.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="89"/>
       <c r="B333" s="74" t="s">
         <v>640</v>
@@ -23141,7 +23197,7 @@
       </c>
       <c r="N451" s="76"/>
     </row>
-    <row r="452" spans="1:14" ht="14.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:14" ht="14.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A452" s="90" t="s">
         <v>906</v>
       </c>
@@ -29164,7 +29220,7 @@
         <v>1280</v>
       </c>
       <c r="D650" s="76" t="s">
-        <v>46</v>
+        <v>286</v>
       </c>
       <c r="E650" s="73"/>
       <c r="F650" s="76" t="s">
@@ -29173,10 +29229,10 @@
       <c r="G650" s="76" t="s">
         <v>49</v>
       </c>
-      <c r="H650" s="76"/>
-      <c r="I650" s="76" t="s">
-        <v>49</v>
-      </c>
+      <c r="H650" s="76" t="s">
+        <v>49</v>
+      </c>
+      <c r="I650" s="76"/>
       <c r="J650" s="76"/>
       <c r="K650" s="76"/>
       <c r="L650" s="76" t="s">
@@ -29959,8 +30015,290 @@
       <c r="M675" s="82"/>
       <c r="N675" s="82"/>
     </row>
+    <row r="676" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="B676" s="82" t="s">
+        <v>1758</v>
+      </c>
+      <c r="C676" s="82" t="s">
+        <v>1757</v>
+      </c>
+      <c r="D676" s="82" t="s">
+        <v>286</v>
+      </c>
+      <c r="E676" s="82" t="s">
+        <v>287</v>
+      </c>
+      <c r="F676" s="82" t="s">
+        <v>1756</v>
+      </c>
+      <c r="G676" s="82" t="s">
+        <v>49</v>
+      </c>
+      <c r="H676" s="82" t="s">
+        <v>49</v>
+      </c>
+      <c r="I676" s="82"/>
+      <c r="J676" s="82"/>
+      <c r="K676" s="82"/>
+      <c r="L676" s="82"/>
+      <c r="M676" s="82"/>
+      <c r="N676" s="82"/>
+    </row>
+    <row r="677" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="F677" s="56" t="s">
+        <v>1759</v>
+      </c>
+      <c r="G677" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="I677" s="56" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="678" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="F678" s="56" t="s">
+        <v>1760</v>
+      </c>
+      <c r="G678" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="I678" s="56" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="679" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="F679" s="56" t="s">
+        <v>1761</v>
+      </c>
+      <c r="G679" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="I679" s="56" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="680" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="F680" s="56" t="s">
+        <v>1762</v>
+      </c>
+      <c r="G680" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="I680" s="56" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="681" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="F681" s="56" t="s">
+        <v>1763</v>
+      </c>
+      <c r="G681" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="I681" s="56" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="682" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="F682" s="56" t="s">
+        <v>1764</v>
+      </c>
+      <c r="G682" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="I682" s="56" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="683" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="F683" s="56" t="s">
+        <v>1765</v>
+      </c>
+      <c r="G683" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="I683" s="56" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="684" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="F684" s="56" t="s">
+        <v>1766</v>
+      </c>
+      <c r="G684" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="I684" s="56" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="685" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="F685" s="56" t="s">
+        <v>1247</v>
+      </c>
+      <c r="G685" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="I685" s="56" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="686" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="F686" s="56" t="s">
+        <v>1256</v>
+      </c>
+      <c r="G686" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="I686" s="56" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="687" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="F687" s="56" t="s">
+        <v>1264</v>
+      </c>
+      <c r="G687" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="I687" s="56" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="688" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="F688" s="56" t="s">
+        <v>1272</v>
+      </c>
+      <c r="G688" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="I688" s="56" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="689" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F689" s="56" t="s">
+        <v>1767</v>
+      </c>
+      <c r="G689" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="I689" s="56" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="690" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F690" s="56" t="s">
+        <v>1768</v>
+      </c>
+      <c r="G690" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="I690" s="56" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="691" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F691" s="56" t="s">
+        <v>1769</v>
+      </c>
+      <c r="G691" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="I691" s="56" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="692" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F692" s="56" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G692" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="I692" s="56" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="693" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F693" s="56" t="s">
+        <v>1260</v>
+      </c>
+      <c r="G693" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="I693" s="56" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="694" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F694" s="56" t="s">
+        <v>1268</v>
+      </c>
+      <c r="G694" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="I694" s="56" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="695" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F695" s="56" t="s">
+        <v>1276</v>
+      </c>
+      <c r="G695" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="I695" s="56" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="696" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F696" s="56" t="s">
+        <v>1770</v>
+      </c>
+      <c r="G696" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="I696" s="56" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="697" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F697" s="56" t="s">
+        <v>1771</v>
+      </c>
+      <c r="G697" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="H697" s="56" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="698" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F698" s="56" t="s">
+        <v>1772</v>
+      </c>
+      <c r="G698" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="H698" s="56" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="699" spans="6:9" x14ac:dyDescent="0.35">
+      <c r="F699" s="56" t="s">
+        <v>1773</v>
+      </c>
+      <c r="G699" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="H699" s="56" t="s">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N675" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A2:N676" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="13">
     <mergeCell ref="A665:A675"/>
     <mergeCell ref="A654:A664"/>
@@ -29976,6 +30314,7 @@
     <mergeCell ref="A205:A322"/>
     <mergeCell ref="A323:A333"/>
   </mergeCells>
+  <phoneticPr fontId="16" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K499:K502 K6:M139 M140:M322 K140:L333 K505:M573 K334:M498" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"OK, COMENTARIO"</formula1>
@@ -29988,16 +30327,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Z238"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="47.54296875" customWidth="1"/>
-    <col min="3" max="3" width="21.36328125" customWidth="1"/>
-    <col min="4" max="4" width="14.36328125" customWidth="1"/>
-    <col min="5" max="5" width="49.6328125" customWidth="1"/>
-    <col min="6" max="6" width="14.08984375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="21.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.453125" customWidth="1"/>
+    <col min="4" max="4" width="14.453125" customWidth="1"/>
+    <col min="5" max="5" width="49.54296875" customWidth="1"/>
+    <col min="6" max="6" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="21.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
@@ -32312,7 +32651,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.36328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="5" width="34.453125" customWidth="1"/>
   </cols>
@@ -32354,15 +32693,15 @@
   <dimension ref="A1:I653"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="62.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="62.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.453125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.54296875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="30.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
